--- a/artfynd/A 3573-2026 artfynd.xlsx
+++ b/artfynd/A 3573-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116435766</v>
+        <v>119029111</v>
       </c>
       <c r="B2" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415246</v>
+        <v>415259</v>
       </c>
       <c r="R2" t="n">
-        <v>6575172</v>
+        <v>6575189</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,29 +740,34 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Eventuellt spår av jättesvampmal i fnöskticka på björklåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -796,59 +787,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116435535</v>
+        <v>119028323</v>
       </c>
       <c r="B3" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415243</v>
+        <v>415252</v>
       </c>
       <c r="R3" t="n">
-        <v>6575173</v>
+        <v>6575168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119028323</v>
+        <v>119028332</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,14 +953,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415252</v>
+        <v>415263</v>
       </c>
       <c r="R4" t="n">
-        <v>6575168</v>
+        <v>6575176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,12 +1032,7 @@
         <v>119028761</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1074,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1169,15 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119030007</v>
+        <v>119029151</v>
       </c>
       <c r="B6" t="n">
-        <v>58164</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,21 +1161,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1214,19 +1190,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415320</v>
+        <v>415247</v>
       </c>
       <c r="R6" t="n">
-        <v>6575199</v>
+        <v>6575194</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,50 +1271,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119028827</v>
+        <v>119029385</v>
       </c>
       <c r="B7" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415244</v>
+        <v>415155</v>
       </c>
       <c r="R7" t="n">
-        <v>6575232</v>
+        <v>6575245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,12 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Nära en liten nedfallen gran, se bild</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,59 +1392,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119029491</v>
+        <v>119029519</v>
       </c>
       <c r="B8" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415172</v>
+        <v>415163</v>
       </c>
       <c r="R8" t="n">
-        <v>6575265</v>
+        <v>6575274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,24 +1474,9 @@
           <t>2024-08-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Vid foten av en björk, se bild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,15 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119029151</v>
+        <v>119029850</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,14 +1548,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415247</v>
+        <v>415293</v>
       </c>
       <c r="R9" t="n">
-        <v>6575194</v>
+        <v>6575221</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1637,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,15 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119029385</v>
+        <v>119030007</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,26 +1635,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1709,19 +1664,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415155</v>
+        <v>415320</v>
       </c>
       <c r="R10" t="n">
-        <v>6575245</v>
+        <v>6575199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1753,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1763,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,59 +1745,62 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119028529</v>
+        <v>119028394</v>
       </c>
       <c r="B11" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>415236</v>
+        <v>415257</v>
       </c>
       <c r="R11" t="n">
-        <v>6575165</v>
+        <v>6575199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1887,17 +1845,13 @@
           <t>10:54</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ganska nära en stor sten.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1916,64 +1870,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119029519</v>
+        <v>116435535</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>årsunge</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>415163</v>
+        <v>415243</v>
       </c>
       <c r="R12" t="n">
-        <v>6575274</v>
+        <v>6575173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2000,12 +1944,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2029,6 +1983,588 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>116435698</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>415246</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6575172</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119028529</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>415236</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6575165</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ganska nära en stor sten.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>119028827</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>415244</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6575232</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Nära en liten nedfallen gran, se bild</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119028980</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>415264</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6575153</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119029491</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>415172</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6575265</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Vid foten av en björk, se bild.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3573-2026 artfynd.xlsx
+++ b/artfynd/A 3573-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029111</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028323</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028332</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028761</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029151</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029385</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029519</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029850</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1742,6 +1787,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119030007</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1867,6 +1917,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028394</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1983,6 +2038,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116435535</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2095,6 +2155,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116435698</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2216,6 +2281,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028529</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2328,6 +2398,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028827</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2444,6 +2519,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028980</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2565,8 +2645,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>